--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedLKFResponse</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedLKFResponse</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -458,7 +458,7 @@
     <t>FehlerWarnung</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fehlerWarnung}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-fehlerWarnung}
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>DiagnoseKnoten</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnoseKnoten}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-diagnoseKnoten}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>LKFPunkte</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-LKFPunkte}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-LKFPunkte}
 </t>
   </si>
   <si>
@@ -503,7 +503,7 @@
     <t>LDFPunktewertNetto</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-LDFPunktewertNetto}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-LDFPunktewertNetto}
 </t>
   </si>
   <si>
@@ -519,7 +519,7 @@
     <t>LDFBetragNetto</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-LDFBetragNetto}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-LDFBetragNetto}
 </t>
   </si>
   <si>
@@ -535,7 +535,7 @@
     <t>PatientenanteilAngehoerige</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-PatientenanteilAngehoerige}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-PatientenanteilAngehoerige}
 </t>
   </si>
   <si>
@@ -551,7 +551,7 @@
     <t>Patientenanteil</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Patientenanteil}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-Patientenanteil}
 </t>
   </si>
   <si>
@@ -567,7 +567,7 @@
     <t>Beihilfenaequivalent</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Beihilfenaequivalent}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-Beihilfenaequivalent}
 </t>
   </si>
   <si>
@@ -580,7 +580,7 @@
     <t>ForderungsbetragAuslaenderverrechnungRegress</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-ForderungsbetragAuslaenderverrechnungRegress}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-ForderungsbetragAuslaenderverrechnungRegress}
 </t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>RechnungsnummerKHLGF</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-RechnungsnummerKHLGF}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-RechnungsnummerKHLGF}
 </t>
   </si>
   <si>
@@ -628,7 +628,7 @@
     <t>Sonderleistungsnummer</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Sonderleistungsnummer}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-Sonderleistungsnummer}
 </t>
   </si>
   <si>
@@ -641,7 +641,7 @@
     <t>AnzahlSonderleistungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AnzahlSonderleistungen}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AnzahlSonderleistungen}
 </t>
   </si>
   <si>
@@ -657,7 +657,7 @@
     <t>PunkteLDFPauschale</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-PunkteLDFPauschale}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-PunkteLDFPauschale}
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
     <t>KonstenmeldungARK</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-KonstenmeldungARK}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-KonstenmeldungARK}
 </t>
   </si>
   <si>
@@ -1109,7 +1109,7 @@
     <t>ClaimResponse.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedLKFRequest)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedLKFRequest)
 </t>
   </si>
   <si>
@@ -1326,7 +1326,7 @@
     <t>Required to relate the current diagnosis to a package billing code that is then referenced on the individual claim items which are specific to the health condition covered by the package code.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
   </si>
   <si>
     <t>ClaimResponse.item</t>
@@ -2534,7 +2534,7 @@
     <t>ClaimResponse.insurance.coverage</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedCoverage)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedCoverage)
 </t>
   </si>
   <si>
@@ -2960,7 +2960,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.25390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.9609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2975,7 +2975,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.26953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedLKFResponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
